--- a/bench/data/files/synthetic2_C.xlsx
+++ b/bench/data/files/synthetic2_C.xlsx
@@ -577,123 +577,123 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Atlas Ltd</t>
+          <t>Wavelength SA</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>2011-01-26</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr"/>
+          <t>2012-06-03</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>2019-04-09</t>
+        </is>
+      </c>
       <c r="G6" s="5" t="n">
-        <v>506.2</v>
+        <v>130</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v/>
+        <v>226.6</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>82.8</v>
+        <v>28.1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v/>
+        <v>61.1</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>260.3</v>
+        <v>121</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>0.441</v>
+        <v>0.87</v>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>Christopher Evans, Olivia Fischer, Matthew Brown</t>
+          <t>Thomas Yamamoto, Amanda Fischer, Michael Vega</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Cobalt Health</t>
+          <t>Fathom Bio</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>2010-02-04</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>2015-12-08</t>
-        </is>
-      </c>
+          <t>2012-04-10</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="5" t="n">
-        <v>1528.6</v>
+        <v>159.7</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>3595.5</v>
+        <v/>
       </c>
       <c r="I7" s="5" t="n">
-        <v>181.7</v>
+        <v>25.6</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>413.5</v>
+        <v/>
       </c>
       <c r="K7" s="5" t="n">
-        <v>196.8</v>
+        <v>29.3</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>0.412</v>
+        <v>0.624</v>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>Sophie Lopez, David Rossi, Thomas Tanaka, Olivia Nakamura, Robert Ueno</t>
+          <t>Priya Hassan, Thomas Johnson, Ravi Vega</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Iris Networks</t>
+          <t>Nimbus Corp</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -703,52 +703,52 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>2013-01-26</t>
+          <t>2013-02-12</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2020-11-14</t>
+          <t>2016-01-30</t>
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>250.3</v>
+        <v>1023.5</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>265.1</v>
+        <v>1906.1</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>24.3</v>
+        <v>210.4</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>21.9</v>
+        <v>370.2</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>32.4</v>
+        <v>906.2</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0.414</v>
+        <v>0.664</v>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>Olivia Yamamoto, David Williams, Michael Chen, Thomas Gupta, Emma Ivanov</t>
+          <t>Sophie Zhang, Sarah Evans, Wei Xu, Matthew Schmidt, Mark Williams</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Lumen Pharma</t>
+          <t>Glacier Partners</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -758,52 +758,52 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>2010-06-22</t>
+          <t>2010-02-10</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2015-06-27</t>
+          <t>2017-02-27</t>
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>126</v>
+        <v>248</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>291.2</v>
+        <v>233.6</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>21.1</v>
+        <v>56</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>33.5</v>
+        <v>138.5</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>93.59999999999999</v>
+        <v>36.9</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.988</v>
+        <v>0.614</v>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>Sarah Williams, Laura Vega, Laura Zhang</t>
+          <t>Ahmed Ueno, James Zhang, Laura Mueller, Olivia Brown, Laura Fischer</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Mosaic Foods</t>
+          <t>Drift Pharma</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -813,52 +813,52 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>2013-11-21</t>
+          <t>2013-04-22</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2019-10-28</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>995.4</v>
+        <v>548.1</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>2197</v>
+        <v>1131.5</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>156.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>363.8</v>
+        <v>127.2</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>576.3</v>
+        <v>407.2</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0.633</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>Matthew Schmidt, Thomas Yamamoto, Mark Vega</t>
+          <t>Elena Davis, Robert Ueno, Hannah Mueller</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Krypton Dynamics</t>
+          <t>Echo Systems</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -868,52 +868,52 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>2010-06-15</t>
+          <t>2012-06-10</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2014-06-02</t>
+          <t>2018-05-05</t>
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>276.7</v>
+        <v>893.8</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>476</v>
+        <v>660.6</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>42.8</v>
+        <v>219</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>98.90000000000001</v>
+        <v>352.7</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>124.4</v>
+        <v>256</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.429</v>
+        <v>0.677</v>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Sarah Evans, Sarah Chen, Andrew Rossi, Sophie Ivanov</t>
+          <t>Elena Kim, Thomas Hassan, Amanda Brown, Wei Yamamoto</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Gravity Media</t>
+          <t>Nova Bio</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -923,52 +923,52 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>2012-07-03</t>
+          <t>2013-01-11</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2017-07-30</t>
+          <t>2018-01-16</t>
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>604</v>
+        <v>981</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>1843.5</v>
+        <v>2774.5</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>119.9</v>
+        <v>139.8</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>178.9</v>
+        <v>314.7</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>505.4</v>
+        <v>459.2</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0.37</v>
+        <v>0.791</v>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>Wei O'Brien, Sarah Kim, Mark Patel</t>
+          <t>Christopher Mueller, Christopher Davis</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Indigo Tech</t>
+          <t>Atlas Media</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -978,52 +978,52 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>2010-07-01</t>
+          <t>2012-02-20</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2015-04-04</t>
+          <t>2015-02-21</t>
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>90.90000000000001</v>
+        <v>1533.9</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>269</v>
+        <v>5249.2</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>24.1</v>
+        <v>343.2</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>34.9</v>
+        <v>724.5</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>54.1</v>
+        <v>1108.3</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>0.629</v>
+        <v>0.625</v>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>Priya Schmidt, James Rossi</t>
+          <t>Sophie Yamamoto, Hannah Gupta, Robert Mueller</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Tessera Capital</t>
+          <t>Wavelength Networks</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1033,52 +1033,52 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>2012-07-08</t>
+          <t>2012-03-27</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
+          <t>2016-02-21</t>
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1068.9</v>
+        <v>1297.5</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>997</v>
+        <v>1969.1</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>174.4</v>
+        <v>131.2</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>254.6</v>
+        <v>197.7</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>412.6</v>
+        <v>208.9</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>0.414</v>
+        <v>0.16</v>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>Emma Lopez, Yuki Kim, Ravi Williams, Ahmed Vega, Priya Zhang</t>
+          <t>Ahmed Tanaka, Christopher Yamamoto</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Meridian Labs</t>
+          <t>Forge Group</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1088,52 +1088,52 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>2010-07-08</t>
+          <t>2011-06-13</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
+          <t>2016-03-19</t>
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1162.1</v>
+        <v>401.1</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>3593.6</v>
+        <v>1043.3</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>131.9</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>211.9</v>
+        <v>153</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>345.2</v>
+        <v>164.1</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>0.355</v>
+        <v>0.699</v>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>Hannah Williams, Amanda Ueno, Jessica Chen, Thomas Schmidt, David Mueller</t>
+          <t>Laura Hassan, Laura Chen</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Echo Group</t>
+          <t>Radial Media</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1143,42 +1143,42 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>2013-09-03</t>
+          <t>2010-02-09</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
+          <t>2012-11-14</t>
         </is>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1995.3</v>
+        <v>1325.7</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>5958.7</v>
+        <v>1558.4</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>185.3</v>
+        <v>253</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>278.5</v>
+        <v>312.5</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>309.5</v>
+        <v>959.4</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0.957</v>
+        <v>0.75</v>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>Emma Zhang, Elena Tanaka, Hannah Hassan</t>
+          <t>Priya Ivanov, Daniel Vega, Rachel Yamamoto, Christopher O'Brien, Emma Tanaka</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Krypton Materials</t>
+          <t>Vertex Dynamics</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1198,136 +1198,132 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>2013-02-05</t>
+          <t>2013-12-05</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2018-12-26</t>
+          <t>2020-11-06</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1530.5</v>
+        <v>175.1</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>2316.2</v>
+        <v>609.2</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>215.6</v>
+        <v>28.4</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>520.1</v>
+        <v>49.6</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>547.7</v>
+        <v>20.7</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.861</v>
+        <v>0.434</v>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>Robert Davis, Rachel Lopez, James Tanaka</t>
+          <t>Andrew Brown, Daniel Fischer, Ravi Tanaka, Ravi Patel</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Fathom Dynamics</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Singapore, SG</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>2011-04-04</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="n">
+        <v>1731.2</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>392.6</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v/>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>1169.5</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Anderson, Olivia Kim, Mark Lopez, Hannah Kim, Amanda Patel</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Fund I Average</t>
         </is>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>844.6</v>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>1982.1</v>
-      </c>
-      <c r="I18" s="7" t="n">
-        <v>113.3</v>
-      </c>
-      <c r="J18" s="7" t="n">
-        <v>219.1</v>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>288.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="G19" s="7" t="n">
+        <v>803.7</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>1578.4</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>154.7</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>254.7</v>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>449.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Fund II</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Meridian Inc</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Munich, DE</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>2012-08-01</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>2017-10-18</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>397.5</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>1378.6</v>
-      </c>
-      <c r="I21" s="5" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>Ravi Evans, Rachel Vega</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Apex Labs</t>
+          <t>Meridian SA</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1337,52 +1333,52 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>2014-07-01</t>
+          <t>2012-06-09</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2018-06-14</t>
+          <t>2015-07-28</t>
         </is>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1964.6</v>
+        <v>1328.1</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>3796.8</v>
+        <v>2172.3</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>396</v>
+        <v>290.2</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>394.8</v>
+        <v>372.7</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>1603.6</v>
+        <v>698.9</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0.304</v>
+        <v>0.254</v>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>Ahmed Gupta, James Fischer, Jessica Anderson, James Lopez, Priya Gupta</t>
+          <t>Wei Mueller, Michael Xu, Andrew Gupta</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Delta Logic</t>
+          <t>Tessera Capital</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1392,52 +1388,52 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>2013-05-13</t>
+          <t>2014-10-26</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2019-04-21</t>
+          <t>2018-08-25</t>
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>1662.7</v>
+        <v>658.4</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>2186.6</v>
+        <v>1258.1</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>246.6</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>502.5</v>
+        <v>132.3</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>323.2</v>
+        <v>291.4</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.374</v>
+        <v>0.304</v>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>Olivia Zhang, Priya Kim, Michael Mueller, Matthew Hassan, Thomas Davis</t>
+          <t>Wei Lopez, Christopher Lopez, Yuki Evans</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Radial Solutions</t>
+          <t>Xenith GmbH</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1447,42 +1443,42 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>2012-07-27</t>
+          <t>2012-07-20</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2018-10-15</t>
+          <t>2015-09-03</t>
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1611.4</v>
+        <v>1540.8</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>2091.7</v>
+        <v>4516.2</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>296.2</v>
+        <v>430.4</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>288.3</v>
+        <v>411.8</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>761.1</v>
+        <v>502.4</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0.991</v>
+        <v>0.262</v>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>Olivia Rossi, Wei Davis</t>
+          <t>Jennifer Ivanov, David Zhang, Emma Evans, Robert Ivanov, Andrew Davis</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Stratus Networks</t>
+          <t>Kepler SA</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -1492,7 +1488,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1502,132 +1498,272 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>2013-10-08</t>
+          <t>2015-10-01</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2019-12-07</t>
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1677.5</v>
+        <v>1625</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>3815.6</v>
+        <v>4931.7</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>165.3</v>
+        <v>415.6</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>398.2</v>
+        <v>626.5</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>737.9</v>
+        <v>282.1</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.229</v>
+        <v>0.336</v>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>Andrew Johnson, Thomas Yamamoto, James Patel, James Johnson, Priya Yamamoto</t>
+          <t>Olivia Vega, Jennifer Kim, Jessica Gupta</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Tessera Logic</t>
+          <t>Fathom Health</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>2015-01-08</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr"/>
+          <t>2014-09-15</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>2020-07-26</t>
+        </is>
+      </c>
       <c r="G26" s="5" t="n">
-        <v>497.7</v>
+        <v>533</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v/>
+        <v>1733.2</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>110.3</v>
+        <v>145.3</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v/>
+        <v>116.7</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>56.8</v>
+        <v>197.8</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>0.346</v>
+        <v>0.862</v>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>Hannah Davis, Rachel Evans, Christopher Anderson, Amanda Gupta</t>
+          <t>David Hassan, Robert Lopez, David Kim, Ahmed Johnson, Emma Ueno</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Fund II Average</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="n">
-        <v>1301.9</v>
-      </c>
-      <c r="H27" s="7" t="n">
-        <v>2653.9</v>
-      </c>
-      <c r="I27" s="7" t="n">
-        <v>208.6</v>
-      </c>
-      <c r="J27" s="7" t="n">
-        <v>324.9</v>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>592</v>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Junction Solutions</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>2012-04-20</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>2018-03-06</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>174.5</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>372.2</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>Laura Xu, Daniel Schmidt, Rachel Ivanov</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Radial GmbH</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>2015-06-26</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>246.9</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>556.5</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>Matthew Anderson, Thomas Tanaka, Emma Evans, Laura Chen, Priya Rossi</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Fund III</t>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Drift Media</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Sydney, AU</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>2013-09-02</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>2016-06-19</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>1316</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>2981.7</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>171.1</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>359.1</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>348.1</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>Ahmed Tanaka, Jennifer Mueller, Ravi Rossi, David Brown</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Indigo Group</t>
+          <t>Krypton Foods</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1637,52 +1773,52 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>2017-12-09</t>
+          <t>2013-07-13</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2016-07-22</t>
         </is>
       </c>
       <c r="G30" s="5" t="n">
-        <v>1893.4</v>
+        <v>490.5</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>3861.7</v>
+        <v>1523.3</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>280.3</v>
+        <v>55.7</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>225.8</v>
+        <v>131</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>369.5</v>
+        <v>208</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>0.991</v>
+        <v>0.219</v>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>Daniel Schmidt, Sophie Yamamoto, Ravi Tanaka, Matthew Kim</t>
+          <t>Elena Kim, David Fischer</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Nimbus Logic</t>
+          <t>Ember GmbH</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -1692,52 +1828,52 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>2017-12-26</t>
+          <t>2015-07-24</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2019-10-15</t>
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>1612.5</v>
+        <v>928.8</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>5117.3</v>
+        <v>2224.6</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>291.9</v>
+        <v>194.2</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>257.8</v>
+        <v>432.4</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>896.7</v>
+        <v>601.9</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>0.194</v>
+        <v>0.332</v>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>Andrew Lopez, Jessica Ueno</t>
+          <t>Thomas Patel, Christopher O'Brien, Emma Gupta, Sarah Kim, Christopher Johnson</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Umbra Foods</t>
+          <t>Beacon Ltd</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -1747,52 +1883,52 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>2015-07-14</t>
+          <t>2012-12-23</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2018-07-07</t>
+          <t>2019-10-13</t>
         </is>
       </c>
       <c r="G32" s="5" t="n">
-        <v>583</v>
+        <v>1647.6</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>1980.5</v>
+        <v>1774.9</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>86.09999999999999</v>
+        <v>460.5</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>163.8</v>
+        <v>1072.6</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>228.4</v>
+        <v>1815.6</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.318</v>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>Emma Schmidt, Robert Kim</t>
+          <t>Priya Johnson, Sophie Evans, Elena Fischer, Daniel Chen, Ahmed Rossi</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Radial Labs</t>
+          <t>Umbra Solutions</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -1802,42 +1938,42 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>2016-11-09</t>
+          <t>2015-01-18</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2021-08-12</t>
+          <t>2020-04-03</t>
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>483.6</v>
+        <v>1071.4</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>1072.3</v>
+        <v>3422.1</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>73.5</v>
+        <v>158.9</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>136.3</v>
+        <v>155.5</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>257.3</v>
+        <v>481.8</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0.969</v>
+        <v>0.238</v>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Ravi Nakamura, Yuki Williams, Laura Kim, Olivia Vega, Hannah Brown</t>
+          <t>Priya Qureshi, Matthew Lopez, Ravi Johnson, Rachel Williams</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Iris Capital</t>
+          <t>Cipher Tech</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -1847,7 +1983,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -1857,52 +1993,52 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>2017-06-25</t>
+          <t>2014-12-11</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2022-06-05</t>
+          <t>2023-01-30</t>
         </is>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1457.2</v>
+        <v>1602.1</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>1600</v>
+        <v>2516.6</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>242.6</v>
+        <v>253</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>578.2</v>
+        <v>481.9</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>905.3</v>
+        <v>322</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>0.371</v>
+        <v>0.667</v>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>Hannah Zhang, Thomas Mueller, Rachel Johnson</t>
+          <t>Sarah Fischer, Michael Mueller, Laura Rossi</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Forge Media</t>
+          <t>Meridian Bio</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -1912,213 +2048,81 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>2015-04-27</t>
+          <t>2015-09-03</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2021-02-07</t>
+          <t>2022-09-10</t>
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>992.3</v>
+        <v>945.4</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>733.7</v>
+        <v>2741.7</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>133.3</v>
+        <v>146.7</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>290.2</v>
+        <v>358.1</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>494.4</v>
+        <v>424.1</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0.774</v>
+        <v>0.879</v>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>Ahmed Vega, Robert Tanaka, Andrew Ueno, David Davis</t>
+          <t>Matthew Evans, Emma Xu, Sarah Kim, Jessica Lopez</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Lattice Ltd</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Zurich, CH</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>2014-09-25</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>2018-09-27</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>1511.7</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>1195.9</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>215.8</v>
-      </c>
-      <c r="J36" s="5" t="n">
-        <v>247.3</v>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>744</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>Robert Hassan, Jessica Patel, David Anderson, Olivia Tanaka</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Nova Capital</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Chicago, IL</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>2015-07-15</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>697.3</v>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>1148.4</v>
-      </c>
-      <c r="I37" s="5" t="n">
-        <v>126.4</v>
-      </c>
-      <c r="J37" s="5" t="n">
-        <v>312.6</v>
-      </c>
-      <c r="K37" s="5" t="n">
-        <v>282.5</v>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>James Chen, Sophie Kim, Michael Hassan</t>
-        </is>
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Fund II Average</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>1007.8</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>2337.5</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>205.3</v>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>341.5</v>
+      </c>
+      <c r="K36" s="7" t="n">
+        <v>452.4</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Orion GmbH</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Zurich, CH</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>Unrealized</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>2016-10-10</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr"/>
-      <c r="G38" s="5" t="n">
-        <v>565.1</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>126.9</v>
-      </c>
-      <c r="J38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K38" s="5" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v>0.6830000000000001</v>
-      </c>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>Hannah Fischer, Michael Fischer, Sarah Patel, Mark Qureshi</t>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Fund III</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Echo Networks</t>
+          <t>Atlas Materials</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -2128,81 +2132,217 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>2015-11-19</t>
+          <t>2016-08-24</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2020-09-12</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>387.7</v>
+        <v>55.7</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>886.1</v>
+        <v>134.4</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>41.7</v>
+        <v>6.2</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>93.8</v>
+        <v>14.4</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>126.9</v>
+        <v>19.7</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0.42</v>
+        <v>0.462</v>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>Rachel Mueller, Mark Zhang, Jessica Nakamura, Priya Patel</t>
+          <t>Laura Chen, Andrew Schmidt, Jennifer Rossi</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Fund III Average</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="n">
-        <v>1018.4</v>
-      </c>
-      <c r="H40" s="7" t="n">
-        <v>1955.1</v>
-      </c>
-      <c r="I40" s="7" t="n">
-        <v>161.9</v>
-      </c>
-      <c r="J40" s="7" t="n">
-        <v>256.2</v>
-      </c>
-      <c r="K40" s="7" t="n">
-        <v>437</v>
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Xenith AG</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>2017-08-18</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>1756.2</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>2813.1</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>466.6</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>688.7</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>1362.8</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>Sophie Ueno, Jessica Davis, Laura Brown, Jessica Fischer</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Ember Materials</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo, JP</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>2015-11-20</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>442.7</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>1487.2</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>Priya Schmidt, Hannah O'Brien, Ahmed Williams</t>
+        </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Fund IV</t>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Wavelength Industries</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo, JP</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>2018-12-04</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>702.5</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>819.9</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>221.1</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>315.6</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>Thomas Xu, Amanda Kim, Andrew Fischer, Hannah Schmidt</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Orion Corp</t>
+          <t>Umbra Foods</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -2212,162 +2352,154 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>2017-12-06</t>
+          <t>2014-03-02</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2023-02-13</t>
+          <t>2017-05-29</t>
         </is>
       </c>
       <c r="G43" s="5" t="n">
-        <v>497.5</v>
+        <v>177</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>1485</v>
+        <v>538.5</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>115.5</v>
+        <v>21</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>117.3</v>
+        <v>34.7</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>368.5</v>
+        <v>39.4</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>0.419</v>
+        <v>0.243</v>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>Ahmed Yamamoto, Andrew Johnson, Emma Lopez</t>
+          <t>Amanda Davis, Thomas Brown, Robert O'Brien, Daniel Davis</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Quanta Energy</t>
+          <t>Nova Systems</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>2016-11-16</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>2023-12-13</t>
-        </is>
-      </c>
+          <t>2015-02-08</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr"/>
       <c r="G44" s="5" t="n">
-        <v>69.3</v>
+        <v>1579.4</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>144.3</v>
+        <v/>
       </c>
       <c r="I44" s="5" t="n">
-        <v>10</v>
+        <v>373.4</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>19.5</v>
+        <v/>
       </c>
       <c r="K44" s="5" t="n">
-        <v>20.2</v>
+        <v>1293.5</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>0.446</v>
+        <v>0.633</v>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>Wei Johnson, Rachel Mueller, Emma Anderson</t>
+          <t>Ahmed Johnson, Mark Qureshi</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Polaris Materials</t>
+          <t>Tessera Group</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>2018-09-25</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>2021-12-15</t>
-        </is>
-      </c>
+          <t>2016-12-20</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="5" t="n">
-        <v>954.8</v>
+        <v>1791.7</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>2761.5</v>
+        <v/>
       </c>
       <c r="I45" s="5" t="n">
-        <v>133.8</v>
+        <v>353</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>291.7</v>
+        <v/>
       </c>
       <c r="K45" s="5" t="n">
-        <v>229.7</v>
+        <v>870.7</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>0.452</v>
+        <v>0.427</v>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Christopher Evans, James Kim</t>
+          <t>Ravi Fischer, Jessica Williams, Mark Xu</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Ember Ltd</t>
+          <t>Echo Energy</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -2377,52 +2509,52 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>2017-11-22</t>
+          <t>2014-02-28</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2020-04-14</t>
         </is>
       </c>
       <c r="G46" s="5" t="n">
-        <v>1452.2</v>
+        <v>1638.1</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>4858.3</v>
+        <v>1685.9</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>163.6</v>
+        <v>304.5</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>191.7</v>
+        <v>387.8</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>400</v>
+        <v>470</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>0.518</v>
+        <v>0.514</v>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>Ahmed Evans, Matthew Mueller, Thomas Mueller, Jennifer Ivanov, Olivia Ivanov</t>
+          <t>Robert O'Brien, Elena Johnson</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Atlas Labs</t>
+          <t>Stratus Energy</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -2432,52 +2564,52 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>2018-12-18</t>
+          <t>2017-05-10</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2022-03-07</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="G47" s="5" t="n">
-        <v>849</v>
+        <v>1598.6</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>2050.9</v>
+        <v>2975.4</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>152.9</v>
+        <v>151.5</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>305.6</v>
+        <v>340</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>182.1</v>
+        <v>296.4</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>0.742</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>Amanda Kim, Elena Fischer</t>
+          <t>Thomas Patel, Laura Xu</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Echo GmbH</t>
+          <t>Radial Corp</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -2487,213 +2619,81 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>2019-07-07</t>
+          <t>2015-09-19</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="G48" s="5" t="n">
-        <v>1549.6</v>
+        <v>862.6</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>5186.4</v>
+        <v>1908.7</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>374</v>
+        <v>112.1</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>867.9</v>
+        <v>213.2</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>1081.1</v>
+        <v>431.1</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>0.901</v>
+        <v>0.437</v>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Yuki Ivanov, Andrew O'Brien</t>
+          <t>Thomas Fischer, Daniel Mueller, Mark Mueller</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Lattice Systems</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>2019-04-20</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>2023-04-05</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>95.2</v>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>240.8</v>
-      </c>
-      <c r="I49" s="5" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="J49" s="5" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="K49" s="5" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="L49" s="5" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="M49" s="5" t="inlineStr">
-        <is>
-          <t>Wei Johnson, Yuki Williams, James Chen, Olivia Ivanov</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>Cobalt Ltd</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>Boston, MA</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>Unrealized</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>2016-06-23</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr"/>
-      <c r="G50" s="5" t="n">
-        <v>1689.9</v>
-      </c>
-      <c r="H50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I50" s="5" t="n">
-        <v>322.4</v>
-      </c>
-      <c r="J50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K50" s="5" t="n">
-        <v>987.4</v>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v>0.574</v>
-      </c>
-      <c r="M50" s="5" t="inlineStr">
-        <is>
-          <t>James Davis, Emma Xu</t>
-        </is>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Fund III Average</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>1060.5</v>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>1545.4</v>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>201.9</v>
+      </c>
+      <c r="J49" s="7" t="n">
+        <v>248.6</v>
+      </c>
+      <c r="K49" s="7" t="n">
+        <v>528.9</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>Bloom Health</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>Seattle, WA</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>2018-11-14</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>2024-12-29</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>717</v>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>1651.9</v>
-      </c>
-      <c r="I51" s="5" t="n">
-        <v>178.2</v>
-      </c>
-      <c r="J51" s="5" t="n">
-        <v>235.7</v>
-      </c>
-      <c r="K51" s="5" t="n">
-        <v>748.4</v>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v>0.742</v>
-      </c>
-      <c r="M51" s="5" t="inlineStr">
-        <is>
-          <t>Olivia Johnson, Yuki Ueno, Michael Qureshi, Ravi Gupta, Emma Schmidt</t>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Fund IV</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Forge Solutions</t>
+          <t>Radial Industries</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -2703,81 +2703,217 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>2017-06-16</t>
+          <t>2017-04-06</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2021-04-26</t>
         </is>
       </c>
       <c r="G52" s="5" t="n">
-        <v>975</v>
+        <v>493.9</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>2739.8</v>
+        <v>808.1</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>148.6</v>
+        <v>104.8</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>301.4</v>
+        <v>191.1</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>636.7</v>
+        <v>429</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>0.904</v>
+        <v>0.779</v>
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>Amanda Evans, Robert Johnson, Emma Rossi</t>
+          <t>Sophie Patel, Daniel Davis, Robert Yamamoto, Sarah Zhang, Emma Williams</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Fund IV Average</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="n">
-        <v>885</v>
-      </c>
-      <c r="H53" s="7" t="n">
-        <v>2346.5</v>
-      </c>
-      <c r="I53" s="7" t="n">
-        <v>162.4</v>
-      </c>
-      <c r="J53" s="7" t="n">
-        <v>262.1</v>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>471.4</v>
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Halo Ltd</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>2019-08-01</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>491</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>608.8</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>198.3</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>174.6</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>Sophie Ivanov, Emma Lopez, James Nakamura, David Hassan</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Apex SA</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>2016-08-07</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>2019-08-24</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>589.9</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>1664.3</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>156.2</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>250.9</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>270</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Ivanov, Ravi Anderson, Sarah Yamamoto, Jennifer Xu, Elena Yamamoto</t>
+        </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>Fund V</t>
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Delta SA</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Paris, FR</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>2016-08-03</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>2023-05-08</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>1736.6</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>4779.3</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>410.8</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>981.5</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>1845.4</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>Christopher Mueller, Mark Kim</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Radial Industries</t>
+          <t>Atlas Networks</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -2787,144 +2923,152 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>2020-01-20</t>
+          <t>2018-06-16</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="G56" s="5" t="n">
-        <v>417.4</v>
+        <v>1567.8</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>1089.2</v>
+        <v>3492.4</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>108.6</v>
+        <v>414.4</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>181</v>
+        <v>797.1</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>135.1</v>
+        <v>1855.4</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.769</v>
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>Sarah Schmidt, Andrew Brown, Hannah Hassan</t>
+          <t>Elena Nakamura, Michael Ueno, Sophie Hassan, Andrew Vega, Daniel Davis</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Tessera AG</t>
+          <t>Yields Health</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>2019-06-06</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr"/>
+          <t>2017-11-28</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
       <c r="G57" s="5" t="n">
-        <v>1493.8</v>
+        <v>1103.1</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v/>
+        <v>2949.8</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>239.2</v>
+        <v>195.7</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v/>
+        <v>460.3</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>523.7</v>
+        <v>103.5</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>0.728</v>
+        <v>0.987</v>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>Ravi Gupta, James Hassan, Matthew Brown</t>
+          <t>David Brown, Thomas Johnson, Wei Ueno, Sophie Johnson, Matthew Tanaka</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Radial GmbH</t>
+          <t>Nimbus Capital</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr"/>
+          <t>2017-07-17</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>2020-05-31</t>
+        </is>
+      </c>
       <c r="G58" s="5" t="n">
-        <v>1884.7</v>
+        <v>1241.8</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v/>
+        <v>2552.8</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>294.9</v>
+        <v>334.9</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v/>
+        <v>477.2</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>1135</v>
+        <v>489.9</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>0.29</v>
+        <v>0.86</v>
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>James Schmidt, Matthew Lopez, Yuki Kim</t>
+          <t>Thomas Rossi, Olivia Zhang</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Glacier Logistics</t>
+          <t>Radial Bio</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -2934,7 +3078,7 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -2944,52 +3088,52 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
+          <t>2017-11-18</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>2022-08-05</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>1901.9</v>
+        <v>1215.8</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>3405.1</v>
+        <v>1468.3</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>311.8</v>
+        <v>146</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>399.7</v>
+        <v>289.8</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>249.4</v>
+        <v>248.8</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>0.466</v>
+        <v>0.41</v>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>Amanda Patel, Thomas Fischer</t>
+          <t>Emma Johnson, Ravi Evans, Yuki Johnson, Olivia Williams</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Delta Pharma</t>
+          <t>Halo Energy</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -2999,213 +3143,81 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>2018-06-11</t>
+          <t>2019-08-05</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>2021-04-27</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="G60" s="5" t="n">
-        <v>112</v>
+        <v>1225.9</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>308.3</v>
+        <v>1913.2</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>11.1</v>
+        <v>278.8</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>18.4</v>
+        <v>647.8</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>35.6</v>
+        <v>524.9</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>0.631</v>
+        <v>0.261</v>
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>Ahmed Mueller, Jessica Mueller, Ravi Patel, Jennifer Brown</t>
+          <t>Michael Vega, Jennifer Fischer</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>Glacier Holdings</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>2018-09-19</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>169.5</v>
-      </c>
-      <c r="H61" s="5" t="n">
-        <v>340.2</v>
-      </c>
-      <c r="I61" s="5" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="J61" s="5" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="K61" s="5" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="L61" s="5" t="n">
-        <v>0.843</v>
-      </c>
-      <c r="M61" s="5" t="inlineStr">
-        <is>
-          <t>Jessica O'Brien, Jennifer Kim, Mark Fischer, Hannah Chen, Mark Nakamura</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>Yields Dynamics</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>Unrealized</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>2020-12-04</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr"/>
-      <c r="G62" s="5" t="n">
-        <v>1951.8</v>
-      </c>
-      <c r="H62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I62" s="5" t="n">
-        <v>360.5</v>
-      </c>
-      <c r="J62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K62" s="5" t="n">
-        <v>213</v>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v>0.856</v>
-      </c>
-      <c r="M62" s="5" t="inlineStr">
-        <is>
-          <t>Elena Hassan, Rachel Tanaka, Mark Vega, James Schmidt, Ahmed Mueller</t>
-        </is>
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Fund IV Average</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="n">
+        <v>1074</v>
+      </c>
+      <c r="H61" s="7" t="n">
+        <v>2248.6</v>
+      </c>
+      <c r="I61" s="7" t="n">
+        <v>241.6</v>
+      </c>
+      <c r="J61" s="7" t="n">
+        <v>477.1</v>
+      </c>
+      <c r="K61" s="7" t="n">
+        <v>660.2</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>Halo Systems</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>2018-05-20</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>623.2</v>
-      </c>
-      <c r="H63" s="5" t="n">
-        <v>1379.1</v>
-      </c>
-      <c r="I63" s="5" t="n">
-        <v>166.1</v>
-      </c>
-      <c r="J63" s="5" t="n">
-        <v>133.5</v>
-      </c>
-      <c r="K63" s="5" t="n">
-        <v>244.4</v>
-      </c>
-      <c r="L63" s="5" t="n">
-        <v>0.658</v>
-      </c>
-      <c r="M63" s="5" t="inlineStr">
-        <is>
-          <t>Wei Kim, Jessica Evans</t>
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Fund V</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Tessera Media</t>
+          <t>Lumen Partners</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -3215,107 +3227,103 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>2019-03-03</t>
+          <t>2019-12-10</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="G64" s="5" t="n">
-        <v>1340.8</v>
+        <v>629.2</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>4028.4</v>
+        <v>2060.3</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>344</v>
+        <v>156</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>605.6</v>
+        <v>239.1</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>576.8</v>
+        <v>258.9</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>0.718</v>
+        <v>0.207</v>
       </c>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>David Chen, Ahmed Williams, Matthew Ivanov, Amanda Schmidt</t>
+          <t>Sophie Patel, Jessica Qureshi</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Wavelength Systems</t>
+          <t>Junction Corp</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
+          <t>2021-03-10</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr"/>
       <c r="G65" s="5" t="n">
-        <v>1384.1</v>
+        <v>240.9</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>2985.1</v>
+        <v/>
       </c>
       <c r="I65" s="5" t="n">
-        <v>264.6</v>
+        <v>19.6</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>513.2</v>
+        <v/>
       </c>
       <c r="K65" s="5" t="n">
-        <v>1070</v>
+        <v>75</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>0.445</v>
+        <v>0.313</v>
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>Ahmed Nakamura, Amanda Qureshi, Emma O'Brien</t>
+          <t>Andrew Anderson, Ravi Kim, Emma Patel</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Indigo Networks</t>
+          <t>Drift Inc</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -3325,52 +3333,52 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>2019-05-23</t>
+          <t>2021-01-09</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="G66" s="5" t="n">
-        <v>1961.7</v>
+        <v>1232.9</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>3298.7</v>
+        <v>1566.2</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>406.3</v>
+        <v>111.9</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>932.3</v>
+        <v>225.5</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>1656.4</v>
+        <v>204.5</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>0.437</v>
+        <v>0.964</v>
       </c>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>Olivia Ivanov, Jennifer Tanaka, Thomas Patel, Olivia Rossi, Andrew Davis</t>
+          <t>Sophie Yamamoto, Thomas Anderson, Ahmed Kim, Emma Ueno, Robert Nakamura</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Ember Capital</t>
+          <t>Bloom Holdings</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -3380,52 +3388,52 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2019-05-26</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2022-07-15</t>
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>1719.7</v>
+        <v>1994.5</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>2867.5</v>
+        <v>4654.2</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>271.8</v>
+        <v>211.9</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>591</v>
+        <v>498.4</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>148.3</v>
+        <v>239.4</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>0.192</v>
+        <v>0.798</v>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>Mark Mueller, Daniel Schmidt, Rachel Ueno, James Vega</t>
+          <t>Hannah Lopez, Olivia Zhang, James Ueno</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Glacier Logic</t>
+          <t>Vertex Holdings</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -3435,52 +3443,52 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>2020-05-04</t>
+          <t>2019-10-18</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="G68" s="5" t="n">
-        <v>367</v>
+        <v>939.1</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>568.3</v>
+        <v>1307.3</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>76.2</v>
+        <v>147</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>116.9</v>
+        <v>201.3</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>76.09999999999999</v>
+        <v>586</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>0.736</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>Amanda Vega, James Rossi, Andrew Anderson, Christopher Ueno, Jennifer Nakamura</t>
+          <t>Matthew Gupta, Andrew O'Brien, Michael Ueno, Amanda O'Brien</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Yields Networks</t>
+          <t>Nimbus Dynamics</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -3490,52 +3498,52 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
+          <t>2019-12-14</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>325.6</v>
+        <v>420.5</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>289.7</v>
+        <v>500.9</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>55.4</v>
+        <v>50.1</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>85.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>129.2</v>
+        <v>72.2</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>0.736</v>
+        <v>0.335</v>
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>Priya Mueller, Ahmed Tanaka</t>
+          <t>David Nakamura, Jessica Xu, Priya Gupta, Ahmed Mueller</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Junction Bio</t>
+          <t>Meridian Capital</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -3545,42 +3553,42 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>2021-12-27</t>
+          <t>2019-11-19</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="G70" s="5" t="n">
-        <v>1851.6</v>
+        <v>289.5</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>4455.5</v>
+        <v>354.9</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>243.6</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>221.5</v>
+        <v>187.1</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>249.5</v>
+        <v>247</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>0.706</v>
+        <v>0.642</v>
       </c>
       <c r="M70" s="5" t="inlineStr">
         <is>
-          <t>Andrew Qureshi, Matthew Schmidt, Ahmed Ivanov, Michael Chen</t>
+          <t>Thomas Gupta, Mark Schmidt, Olivia O'Brien</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Forge Tech</t>
+          <t>Drift Capital</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -3590,7 +3598,7 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -3600,154 +3608,162 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>2020-08-09</t>
+          <t>2020-04-14</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>182.1</v>
+        <v>275.7</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>513.7</v>
+        <v>718.9</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>40.1</v>
+        <v>71</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>81.09999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>88.3</v>
+        <v>212</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>0.571</v>
+        <v>0.851</v>
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>Robert Chen, Elena Vega, Hannah Lopez</t>
+          <t>Robert Rossi, Jessica Chen</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Beacon Ltd</t>
+          <t>Vertex Labs</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
-        </is>
-      </c>
-      <c r="F72" s="5" t="inlineStr"/>
+          <t>2020-10-17</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>2024-09-25</t>
+        </is>
+      </c>
       <c r="G72" s="5" t="n">
-        <v>1517.4</v>
+        <v>1491.3</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v/>
+        <v>1792.3</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>192.8</v>
+        <v>335.6</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v/>
+        <v>327.3</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>782</v>
+        <v>456.9</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>0.486</v>
+        <v>0.27</v>
       </c>
       <c r="M72" s="5" t="inlineStr">
         <is>
-          <t>Wei Kim, Priya Yamamoto, Michael Hassan, Ahmed Gupta, Wei Nakamura</t>
+          <t>Ravi Gupta, Rachel O'Brien</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Yields Ltd</t>
+          <t>Halo Dynamics</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>2019-09-13</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="inlineStr"/>
+          <t>2018-03-26</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
       <c r="G73" s="5" t="n">
-        <v>1203.9</v>
+        <v>1777.6</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v/>
+        <v>3945.7</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>292</v>
+        <v>480.9</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v/>
+        <v>1065.8</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>916.7</v>
+        <v>1329.8</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>0.792</v>
+        <v>0.769</v>
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>Christopher Rossi, Sarah Williams, Emma Schmidt, Matthew Ueno</t>
+          <t>Andrew Anderson, Amanda Hassan, Elena Lopez, Thomas Hassan, Priya Ueno</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Delta Systems</t>
+          <t>Halo Labs</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -3757,42 +3773,42 @@
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>2018-03-11</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>2021-04-19</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="G74" s="5" t="n">
-        <v>1662.6</v>
+        <v>1371</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>3084</v>
+        <v>1898.1</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>411.2</v>
+        <v>191.4</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>782.7</v>
+        <v>188</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>345.9</v>
+        <v>214.5</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>0.679</v>
+        <v>0.287</v>
       </c>
       <c r="M74" s="5" t="inlineStr">
         <is>
-          <t>David Patel, Ravi Kim, Amanda Vega</t>
+          <t>Priya Gupta, Ravi Tanaka, Olivia Ueno, Thomas Gupta</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Helix Ltd</t>
+          <t>Cobalt Logistics</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -3802,7 +3818,7 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -3812,52 +3828,52 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>2018-03-28</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>911.6</v>
+        <v>1172.7</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>1113</v>
+        <v>1544.2</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>235.9</v>
+        <v>220.3</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>236.3</v>
+        <v>412.8</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>634.2</v>
+        <v>757.6</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>0.664</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>James O'Brien, Laura Patel</t>
+          <t>Olivia Evans, Jennifer Kim, Ahmed Nakamura, Laura Patel, Emma Hassan</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Mosaic Dynamics</t>
+          <t>Atlas Partners</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -3867,52 +3883,52 @@
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>2021-01-08</t>
+          <t>2018-11-23</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2022-10-25</t>
         </is>
       </c>
       <c r="G76" s="5" t="n">
-        <v>879.3</v>
+        <v>1399.3</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>1974.2</v>
+        <v>3107.9</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>88.40000000000001</v>
+        <v>330.4</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>121.3</v>
+        <v>515</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>138.9</v>
+        <v>902.1</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>0.394</v>
+        <v>0.798</v>
       </c>
       <c r="M76" s="5" t="inlineStr">
         <is>
-          <t>Rachel Chen, Priya Ivanov, Priya Mueller, Hannah Nakamura</t>
+          <t>Yuki Xu, Hannah Williams, Mark Gupta</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Orion Energy</t>
+          <t>Glacier Networks</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -3922,52 +3938,52 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>779.6</v>
+        <v>1506.3</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>1118.5</v>
+        <v>3282.6</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>135.1</v>
+        <v>162.6</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>238.6</v>
+        <v>200.7</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>135.8</v>
+        <v>298.5</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>0.704</v>
+        <v>0.93</v>
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>Michael Schmidt, Mark Lopez, Ahmed Hassan</t>
+          <t>Yuki Nakamura, Andrew Vega, Christopher O'Brien</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Apex SA</t>
+          <t>Delta Group</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -3977,52 +3993,52 @@
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2020-10-27</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-01-12</t>
         </is>
       </c>
       <c r="G78" s="5" t="n">
-        <v>506.6</v>
+        <v>546.7</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>1458.7</v>
+        <v>383.9</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>104.6</v>
+        <v>141.4</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>106.2</v>
+        <v>212.8</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>351.2</v>
+        <v>246.9</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>0.723</v>
+        <v>0.481</v>
       </c>
       <c r="M78" s="5" t="inlineStr">
         <is>
-          <t>Andrew Lopez, Amanda Vega</t>
+          <t>Jessica Davis, Amanda Hassan</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>Cobalt AG</t>
+          <t>Gravity Inc</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -4032,52 +4048,52 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>2020-11-02</t>
+          <t>2019-05-03</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="G79" s="5" t="n">
-        <v>868.8</v>
+        <v>523.3</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>2296.9</v>
+        <v>786.1</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>128.6</v>
+        <v>123.9</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>269.9</v>
+        <v>256.1</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>118.8</v>
+        <v>367.3</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>0.245</v>
+        <v>0.327</v>
       </c>
       <c r="M79" s="5" t="inlineStr">
         <is>
-          <t>Elena Vega, James O'Brien, Jessica Williams, Mark Kim</t>
+          <t>Emma O'Brien, Sarah Nakamura, Matthew Hassan, Daniel Davis</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Beacon Capital</t>
+          <t>Mosaic Corp</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -4087,86 +4103,90 @@
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-12-09</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>2023-03-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="G80" s="5" t="n">
-        <v>393</v>
+        <v>1920.9</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>578.4</v>
+        <v>4464.6</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>55.8</v>
+        <v>479.4</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>92.09999999999999</v>
+        <v>1108.3</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>231.6</v>
+        <v>1900.2</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>0.914</v>
+        <v>0.473</v>
       </c>
       <c r="M80" s="5" t="inlineStr">
         <is>
-          <t>Laura Anderson, Robert Fischer, Daniel Kim, Michael Lopez, Matthew Zhang</t>
+          <t>Rachel Schmidt, Michael Rossi, Amanda Lopez, Amanda Qureshi</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>Iris SA</t>
+          <t>Orion Bio</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>2020-06-07</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr"/>
+          <t>2019-11-21</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
       <c r="G81" s="5" t="n">
-        <v>1888.3</v>
+        <v>1163</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v/>
+        <v>2897.3</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>370.3</v>
+        <v>212</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v/>
+        <v>486.7</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>634.4</v>
+        <v>910.6</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>0.665</v>
+        <v>0.168</v>
       </c>
       <c r="M81" s="5" t="inlineStr">
         <is>
-          <t>Sarah Lopez, Sarah Davis</t>
+          <t>Elena Fischer, Mark Nakamura, Priya Johnson, Elena Lopez, Rachel Qureshi</t>
         </is>
       </c>
     </row>
@@ -4177,19 +4197,19 @@
         </is>
       </c>
       <c r="G82" s="7" t="n">
-        <v>1088.4</v>
+        <v>1049.7</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>1857.6</v>
+        <v>2074.4</v>
       </c>
       <c r="I82" s="7" t="n">
-        <v>201.6</v>
+        <v>195.6</v>
       </c>
       <c r="J82" s="7" t="n">
-        <v>288.4</v>
+        <v>368.9</v>
       </c>
       <c r="K82" s="7" t="n">
-        <v>417.8</v>
+        <v>515.5</v>
       </c>
     </row>
   </sheetData>
